--- a/data/trans_orig/P04B1_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248277</t>
+          <t>245333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>307543</t>
+          <t>308588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160230</t>
+          <t>160073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207465</t>
+          <t>207293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426982</t>
+          <t>426211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>502195</t>
+          <t>502502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92444</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151710</t>
+          <t>154654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105735</t>
+          <t>105907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152970</t>
+          <t>153127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210992</t>
+          <t>210685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286205</t>
+          <t>286976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235818</t>
+          <t>232583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285422</t>
+          <t>285199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336432</t>
+          <t>337274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>420642</t>
+          <t>420486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589513</t>
+          <t>588464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>706444</t>
+          <t>691553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137960</t>
+          <t>138183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>187564</t>
+          <t>190799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>91607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175661</t>
+          <t>174819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229031</t>
+          <t>243922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>345962</t>
+          <t>347011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>323967</t>
+          <t>324228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>368915</t>
+          <t>366884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>374515</t>
+          <t>372949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447170</t>
+          <t>447619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>711454</t>
+          <t>712554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>799774</t>
+          <t>799324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164201</t>
+          <t>166232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209149</t>
+          <t>208888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143941</t>
+          <t>143492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216596</t>
+          <t>218162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324453</t>
+          <t>324903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412773</t>
+          <t>411673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>570485</t>
+          <t>571994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>783253</t>
+          <t>789346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>426370</t>
+          <t>428080</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>493005</t>
+          <t>494632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020856</t>
+          <t>1017420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1313723</t>
+          <t>1320279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317301</t>
+          <t>315792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218578</t>
+          <t>216951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285213</t>
+          <t>283503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285647</t>
+          <t>279091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578514</t>
+          <t>581950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>346513</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>388479</t>
+          <t>389240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320517</t>
+          <t>324042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356322</t>
+          <t>357052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677023</t>
+          <t>680062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>733906</t>
+          <t>731072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171725</t>
+          <t>170964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213691</t>
+          <t>212535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190963</t>
+          <t>190233</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226768</t>
+          <t>223243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373583</t>
+          <t>376417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430466</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212083</t>
+          <t>213113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241557</t>
+          <t>242318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>381017</t>
+          <t>378335</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>543871</t>
+          <t>539861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>602657</t>
+          <t>604744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>837273</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>125069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155304</t>
+          <t>154274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>68507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227351</t>
+          <t>230033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138482</t>
+          <t>155595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373098</t>
+          <t>371011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155645</t>
+          <t>156221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181892</t>
+          <t>183445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,47 +2803,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>273937</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>259538</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>286527</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>64,33%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>273937</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>259850</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>287881</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>423845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462262</t>
+          <t>461441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100867</t>
+          <t>99314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127114</t>
+          <t>126538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,47 +2916,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>151894</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>139304</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>166293</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>35,67%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,95%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>151894</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>137950</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>165981</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246328</t>
+          <t>247149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>284351</t>
+          <t>284745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2213853</t>
+          <t>2218726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2551761</t>
+          <t>2597903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2369045</t>
+          <t>2370128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2680116</t>
+          <t>2693560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4623740</t>
+          <t>4631446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5098632</t>
+          <t>5102104</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>902861</t>
+          <t>856719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1240769</t>
+          <t>1235896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1029355</t>
+          <t>1015911</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1340426</t>
+          <t>1339343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2065461</t>
+          <t>2061989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2540353</t>
+          <t>2532647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>279914</t>
+          <t>261143</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245333</t>
+          <t>231182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308588</t>
+          <t>290748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>184815</t>
+          <t>205703</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160073</t>
+          <t>178132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207293</t>
+          <t>229559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>464728</t>
+          <t>466846</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426211</t>
+          <t>428020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>502502</t>
+          <t>506721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>146650</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91399</t>
+          <t>117045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>176611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>128385</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105907</t>
+          <t>132953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153127</t>
+          <t>184380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>248459</t>
+          <t>303459</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210685</t>
+          <t>263584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286976</t>
+          <t>342285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>260995</t>
+          <t>287704</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232583</t>
+          <t>258822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285199</t>
+          <t>314053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>368243</t>
+          <t>331293</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>307401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>420486</t>
+          <t>353488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>629238</t>
+          <t>618997</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588464</t>
+          <t>582837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>691553</t>
+          <t>652718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>162387</t>
+          <t>187543</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138183</t>
+          <t>161194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190799</t>
+          <t>216425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>143850</t>
+          <t>170440</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91607</t>
+          <t>148245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>194332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>306237</t>
+          <t>357983</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243922</t>
+          <t>324262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347011</t>
+          <t>394143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>346035</t>
+          <t>395125</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324228</t>
+          <t>369769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366884</t>
+          <t>418258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>400317</t>
+          <t>403167</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372949</t>
+          <t>382526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447619</t>
+          <t>424977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>746352</t>
+          <t>798292</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>712554</t>
+          <t>766727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>799324</t>
+          <t>828251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>187081</t>
+          <t>221545</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166232</t>
+          <t>198412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208888</t>
+          <t>246901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>190794</t>
+          <t>218311</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143492</t>
+          <t>196501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218162</t>
+          <t>238952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>377875</t>
+          <t>439856</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324903</t>
+          <t>409897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>411673</t>
+          <t>471421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533116</t>
+          <t>616670</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533116</t>
+          <t>616670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533116</t>
+          <t>616670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1124227</t>
+          <t>1238148</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124227</t>
+          <t>1238148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1124227</t>
+          <t>1238148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>668087</t>
+          <t>449756</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>571994</t>
+          <t>422876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>789346</t>
+          <t>473162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>451240</t>
+          <t>440182</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>428080</t>
+          <t>417348</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>494632</t>
+          <t>461008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1119327</t>
+          <t>889937</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1017420</t>
+          <t>855987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1320279</t>
+          <t>921014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>219699</t>
+          <t>250861</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>227455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315792</t>
+          <t>277741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>260343</t>
+          <t>295320</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216951</t>
+          <t>274494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283503</t>
+          <t>318154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>480043</t>
+          <t>546182</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279091</t>
+          <t>515105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>581950</t>
+          <t>580132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711583</t>
+          <t>735502</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711583</t>
+          <t>735502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711583</t>
+          <t>735502</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599370</t>
+          <t>1436119</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599370</t>
+          <t>1436119</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599370</t>
+          <t>1436119</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>367758</t>
+          <t>393138</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>371027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>389240</t>
+          <t>417002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>339358</t>
+          <t>369484</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324042</t>
+          <t>350250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357052</t>
+          <t>387091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>707116</t>
+          <t>762621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>680062</t>
+          <t>737031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>731072</t>
+          <t>793947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>192446</t>
+          <t>215127</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170964</t>
+          <t>191263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212535</t>
+          <t>237238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>207927</t>
+          <t>238664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190233</t>
+          <t>221057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>223243</t>
+          <t>257898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>400373</t>
+          <t>453791</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376417</t>
+          <t>422465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>479381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107489</t>
+          <t>1216412</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107489</t>
+          <t>1216412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107489</t>
+          <t>1216412</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>227433</t>
+          <t>252411</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213113</t>
+          <t>235536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242318</t>
+          <t>267394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>460457</t>
+          <t>273765</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>378335</t>
+          <t>260323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>539861</t>
+          <t>289642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>687889</t>
+          <t>526175</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>604744</t>
+          <t>503802</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>820160</t>
+          <t>547346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>139954</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125069</t>
+          <t>138686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154274</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>147911</t>
+          <t>165401</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68507</t>
+          <t>149524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230033</t>
+          <t>178843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>287866</t>
+          <t>319071</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155595</t>
+          <t>297900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>371011</t>
+          <t>341444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367387</t>
+          <t>406080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367387</t>
+          <t>406080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367387</t>
+          <t>406080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975755</t>
+          <t>845246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975755</t>
+          <t>845246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975755</t>
+          <t>845246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>168263</t>
+          <t>181860</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156221</t>
+          <t>167732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183445</t>
+          <t>195719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>273937</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259538</t>
+          <t>279773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286527</t>
+          <t>309570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>442201</t>
+          <t>476170</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>423845</t>
+          <t>452882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461441</t>
+          <t>498833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>128338</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99314</t>
+          <t>114479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126538</t>
+          <t>142466</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>151894</t>
+          <t>170299</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139304</t>
+          <t>155039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>184836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>266389</t>
+          <t>298637</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247149</t>
+          <t>275974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>284745</t>
+          <t>321925</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2318485</t>
+          <t>2221137</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2218726</t>
+          <t>2159459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2597903</t>
+          <t>2279291</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2478366</t>
+          <t>2317903</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2370128</t>
+          <t>2264233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2693560</t>
+          <t>2373117</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4796851</t>
+          <t>4539040</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4631446</t>
+          <t>4459440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5102104</t>
+          <t>4619412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1136137</t>
+          <t>1303734</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856719</t>
+          <t>1245580</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1235896</t>
+          <t>1365412</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1231105</t>
+          <t>1415244</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1015911</t>
+          <t>1360030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1339343</t>
+          <t>1468914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2367242</t>
+          <t>2718978</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2061989</t>
+          <t>2638606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2532647</t>
+          <t>2798578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
